--- a/code/codeForSimulations/Table4/Tab4.xlsx
+++ b/code/codeForSimulations/Table4/Tab4.xlsx
@@ -159,22 +159,22 @@
         <v>50</v>
       </c>
       <c r="E5" s="0">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F5" s="0">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>0</v>
+        <v>0.68000000000000005</v>
       </c>
       <c r="J5" s="0">
-        <v>0</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
@@ -182,22 +182,22 @@
         <v>100</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>0</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>0</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>0</v>
+        <v>0.81000000000000005</v>
       </c>
       <c r="J6" s="0">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="K6" s="0">
-        <v>0</v>
+        <v>0.92000000000000004</v>
       </c>
     </row>
     <row r="7">
@@ -205,22 +205,22 @@
         <v>200</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>0.68999999999999995</v>
       </c>
       <c r="F7" s="0">
-        <v>0</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>0</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>0</v>
+        <v>0.95999999999999996</v>
       </c>
       <c r="J7" s="0">
-        <v>0</v>
+        <v>0.97999999999999998</v>
       </c>
       <c r="K7" s="0">
-        <v>0</v>
+        <v>0.98999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -231,22 +231,22 @@
         <v>50</v>
       </c>
       <c r="E10" s="0">
-        <v>0.65000000000000002</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="F10" s="0">
-        <v>0.73999999999999999</v>
+        <v>0.77000000000000002</v>
       </c>
       <c r="G10" s="0">
-        <v>0.76000000000000001</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="I10" s="0">
-        <v>0.46000000000000002</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="J10" s="0">
-        <v>0.52000000000000002</v>
+        <v>0.53000000000000003</v>
       </c>
       <c r="K10" s="0">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="11">
@@ -254,22 +254,22 @@
         <v>100</v>
       </c>
       <c r="E11" s="0">
-        <v>0.81000000000000005</v>
+        <v>0.87</v>
       </c>
       <c r="F11" s="0">
-        <v>0.92000000000000004</v>
+        <v>0.91000000000000003</v>
       </c>
       <c r="G11" s="0">
         <v>0.93999999999999995</v>
       </c>
       <c r="I11" s="0">
-        <v>0.37</v>
+        <v>0.42999999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>0.45000000000000001</v>
+        <v>0.52000000000000002</v>
       </c>
       <c r="K11" s="0">
-        <v>0.54000000000000004</v>
+        <v>0.60999999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -277,22 +277,22 @@
         <v>200</v>
       </c>
       <c r="E12" s="0">
-        <v>0.91000000000000003</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="F12" s="0">
-        <v>0.88</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="G12" s="0">
         <v>0.95999999999999996</v>
       </c>
       <c r="I12" s="0">
-        <v>0.42999999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="J12" s="0">
-        <v>0.60999999999999999</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K12" s="0">
-        <v>0.66000000000000003</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="15">
@@ -303,22 +303,22 @@
         <v>50</v>
       </c>
       <c r="E15" s="0">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="G15" s="0">
         <v>0.75</v>
       </c>
-      <c r="F15" s="0">
-        <v>0.72999999999999998</v>
-      </c>
-      <c r="G15" s="0">
-        <v>0.78000000000000003</v>
-      </c>
       <c r="I15" s="0">
-        <v>0.45000000000000001</v>
+        <v>0.40999999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>0.53000000000000003</v>
+        <v>0.48999999999999999</v>
       </c>
       <c r="K15" s="0">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -329,16 +329,16 @@
         <v>0.92000000000000004</v>
       </c>
       <c r="F16" s="0">
-        <v>0.95999999999999996</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="G16" s="0">
-        <v>1</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="I16" s="0">
-        <v>0.32000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="J16" s="0">
-        <v>0.48999999999999999</v>
+        <v>0.46000000000000002</v>
       </c>
       <c r="K16" s="0">
         <v>0.54000000000000004</v>
@@ -349,22 +349,22 @@
         <v>200</v>
       </c>
       <c r="E17" s="0">
+        <v>0.93000000000000005</v>
+      </c>
+      <c r="F17" s="0">
         <v>0.94999999999999996</v>
       </c>
-      <c r="F17" s="0">
-        <v>0.92000000000000004</v>
-      </c>
       <c r="G17" s="0">
-        <v>0.98999999999999999</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="I17" s="0">
-        <v>0.28000000000000003</v>
+        <v>0.35999999999999999</v>
       </c>
       <c r="J17" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="K17" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
   </sheetData>
